--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_cg_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_cg_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>11-02-2021 08:30</t>
+          <t>2021-11-02 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="n">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="n">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="n">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2708,7 +2708,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>04-05-2021 08:30</t>
+          <t>2021-04-05 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="n">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>19-08-2021 08:30</t>
+          <t>2021-08-19 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>08-09-2021 08:30</t>
+          <t>2021-08-09 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>16-11-2021 08:30</t>
+          <t>2021-11-16 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>02-12-2021 08:30</t>
+          <t>2021-02-12 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>14-07-2021 08:30</t>
+          <t>2021-07-14 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4434,7 +4434,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>11-08-2021 08:30</t>
+          <t>2021-11-08 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="n">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>08-04-2021 08:30</t>
+          <t>2021-08-04 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="n">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>07-07-2021 08:30</t>
+          <t>2021-07-07 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="inlineStr"/>
@@ -5034,7 +5034,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>10-12-2021 08:30</t>
+          <t>2021-10-12 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="inlineStr"/>
@@ -5131,7 +5131,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="inlineStr"/>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="inlineStr"/>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="inlineStr"/>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="inlineStr"/>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="inlineStr"/>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="inlineStr"/>
@@ -5689,7 +5689,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="inlineStr"/>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="inlineStr"/>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="inlineStr"/>
@@ -5968,7 +5968,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>20-03-2021 08:30</t>
+          <t>2021-03-20 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6154,7 +6154,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="inlineStr"/>
@@ -6340,7 +6340,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="inlineStr"/>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="inlineStr"/>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="inlineStr"/>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="inlineStr"/>
@@ -6991,7 +6991,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="inlineStr"/>
@@ -7084,7 +7084,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7177,7 +7177,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7363,7 +7363,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>13-03-2021 08:30</t>
+          <t>2021-03-13 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="inlineStr"/>
@@ -7456,7 +7456,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>09-01-2021 08:30</t>
+          <t>2021-09-01 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="inlineStr"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="inlineStr"/>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="inlineStr"/>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="inlineStr"/>
@@ -7921,7 +7921,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="inlineStr"/>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8293,7 +8293,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="inlineStr"/>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="inlineStr"/>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="inlineStr"/>
@@ -8572,7 +8572,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="inlineStr"/>
@@ -8665,7 +8665,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="inlineStr"/>
@@ -8758,7 +8758,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="inlineStr"/>
@@ -8851,7 +8851,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="inlineStr"/>
@@ -8944,7 +8944,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="inlineStr"/>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="inlineStr"/>
@@ -9130,7 +9130,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="inlineStr"/>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="inlineStr"/>
@@ -9316,7 +9316,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="inlineStr"/>
@@ -9409,7 +9409,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9595,7 +9595,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -9967,7 +9967,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="inlineStr"/>
@@ -10060,7 +10060,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>27-01-2021 08:30</t>
+          <t>2021-01-27 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="inlineStr"/>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10353,7 +10353,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="inlineStr"/>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>26-02-2021 08:30</t>
+          <t>2021-02-26 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="inlineStr"/>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="inlineStr"/>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="inlineStr"/>
@@ -10729,7 +10729,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="inlineStr"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="inlineStr"/>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="inlineStr"/>
@@ -11020,7 +11020,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="inlineStr"/>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="inlineStr"/>
@@ -11214,7 +11214,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>06-07-2021 08:30</t>
+          <t>2021-06-07 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="inlineStr"/>
@@ -11311,7 +11311,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>04-08-2021 08:30</t>
+          <t>2021-04-08 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="inlineStr"/>
@@ -11408,7 +11408,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>06-09-2021 08:30</t>
+          <t>2021-06-09 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="inlineStr"/>
@@ -11505,7 +11505,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="inlineStr"/>
@@ -11602,7 +11602,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="inlineStr"/>
@@ -11699,7 +11699,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="inlineStr"/>
@@ -11796,7 +11796,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="inlineStr"/>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="inlineStr"/>
@@ -12540,7 +12540,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="inlineStr"/>
@@ -12633,7 +12633,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="inlineStr"/>
@@ -12726,7 +12726,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="inlineStr"/>
@@ -12819,7 +12819,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="inlineStr"/>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -13005,7 +13005,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13098,7 +13098,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13191,7 +13191,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13377,7 +13377,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
@@ -13470,7 +13470,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13563,7 +13563,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="inlineStr"/>
@@ -13842,7 +13842,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="inlineStr"/>
@@ -13935,7 +13935,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="inlineStr"/>
@@ -14028,7 +14028,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="inlineStr"/>
@@ -14121,7 +14121,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="inlineStr"/>
@@ -14214,7 +14214,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="inlineStr"/>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="inlineStr"/>
@@ -14400,7 +14400,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="inlineStr"/>
@@ -14493,7 +14493,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="inlineStr"/>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="inlineStr"/>
@@ -14679,7 +14679,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="inlineStr"/>
@@ -14772,7 +14772,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="inlineStr"/>
@@ -14865,7 +14865,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="inlineStr"/>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="inlineStr"/>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15144,7 +15144,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15237,7 +15237,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>19-02-2021 08:30</t>
+          <t>2021-02-19 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -15795,7 +15795,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -15981,7 +15981,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="inlineStr"/>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -16260,7 +16260,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -16353,7 +16353,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -16539,7 +16539,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>05-03-2021 08:30</t>
+          <t>2021-05-03 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -16725,7 +16725,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>04-01-2021 08:30</t>
+          <t>2021-04-01 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>03-03-2021 08:30</t>
+          <t>2021-03-03 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17113,7 +17113,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>03-05-2021 08:30</t>
+          <t>2021-03-05 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>02-06-2021 08:30</t>
+          <t>2021-02-06 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>05-07-2021 08:30</t>
+          <t>2021-05-07 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>02-08-2021 08:30</t>
+          <t>2021-02-08 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17501,7 +17501,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>02-09-2021 08:30</t>
+          <t>2021-02-09 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>04-10-2021 08:30</t>
+          <t>2021-04-10 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>01-11-2021 08:30</t>
+          <t>2021-01-11 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -17792,7 +17792,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>01-12-2021 08:30</t>
+          <t>2021-01-12 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -17889,7 +17889,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>31-01-2021 08:30</t>
+          <t>2021-01-31 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>13-02-2021 08:30</t>
+          <t>2021-02-13 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18075,7 +18075,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
